--- a/multi seed generators/merged 10 seeds/regression/results/aggregated/privacy_mean_sd.xlsx
+++ b/multi seed generators/merged 10 seeds/regression/results/aggregated/privacy_mean_sd.xlsx
@@ -1682,12 +1682,10 @@
       <c r="O22" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P22" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P22" s="2"/>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ± 0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="R22" s="2" t="n">
@@ -1753,12 +1751,10 @@
       <c r="O23" t="n">
         <v>15.28669699143929</v>
       </c>
-      <c r="P23" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P23"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.2867 ± 0</t>
+          <t xml:space="preserve">15.2867</t>
         </is>
       </c>
       <c r="R23" t="n">
@@ -1824,12 +1820,10 @@
       <c r="O24" s="2" t="n">
         <v>15.28669699143929</v>
       </c>
-      <c r="P24" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P24" s="2"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.2867 ± 0</t>
+          <t xml:space="preserve">15.2867</t>
         </is>
       </c>
       <c r="R24" s="2" t="n">
@@ -1895,12 +1889,10 @@
       <c r="O25" t="n">
         <v>14.47097656386145</v>
       </c>
-      <c r="P25" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P25"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t xml:space="preserve">14.471 ± 0</t>
+          <t xml:space="preserve">14.471</t>
         </is>
       </c>
       <c r="R25" t="n">
@@ -1966,12 +1958,10 @@
       <c r="O26" s="2" t="n">
         <v>0.9447941295445619</v>
       </c>
-      <c r="P26" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P26" s="2"/>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.944794 ± 0</t>
+          <t xml:space="preserve">0.944794</t>
         </is>
       </c>
       <c r="R26" s="2" t="n">
@@ -4522,12 +4512,10 @@
       <c r="O62" s="2" t="n">
         <v>0.7964197530864199</v>
       </c>
-      <c r="P62" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P62" s="2"/>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.79642 ± 0</t>
+          <t xml:space="preserve">0.79642</t>
         </is>
       </c>
       <c r="R62" s="2" t="n">
@@ -4593,12 +4581,10 @@
       <c r="O63" t="n">
         <v>4.773443731055067</v>
       </c>
-      <c r="P63" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P63"/>
       <c r="Q63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.77344 ± 0</t>
+          <t xml:space="preserve">4.77344</t>
         </is>
       </c>
       <c r="R63" t="n">
@@ -4664,12 +4650,10 @@
       <c r="O64" s="2" t="n">
         <v>4.773443731055067</v>
       </c>
-      <c r="P64" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P64" s="2"/>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.77344 ± 0</t>
+          <t xml:space="preserve">4.77344</t>
         </is>
       </c>
       <c r="R64" s="2" t="n">
@@ -4735,12 +4719,10 @@
       <c r="O65" t="n">
         <v>4.260656729701209</v>
       </c>
-      <c r="P65" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P65"/>
       <c r="Q65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.26066 ± 0</t>
+          <t xml:space="preserve">4.26066</t>
         </is>
       </c>
       <c r="R65" t="n">
@@ -4806,12 +4788,10 @@
       <c r="O66" s="2" t="n">
         <v>0.9270333177979528</v>
       </c>
-      <c r="P66" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P66" s="2"/>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.927033 ± 0</t>
+          <t xml:space="preserve">0.927033</t>
         </is>
       </c>
       <c r="R66" s="2" t="n">
@@ -7362,12 +7342,10 @@
       <c r="O102" s="2" t="n">
         <v>0.8809876543209876</v>
       </c>
-      <c r="P102" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P102" s="2"/>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.880988 ± 0</t>
+          <t xml:space="preserve">0.880988</t>
         </is>
       </c>
       <c r="R102" s="2" t="n">
@@ -7433,12 +7411,10 @@
       <c r="O103" t="n">
         <v>415.3891970836409</v>
       </c>
-      <c r="P103" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P103"/>
       <c r="Q103" t="inlineStr">
         <is>
-          <t xml:space="preserve">415.389 ± 0</t>
+          <t xml:space="preserve">415.389</t>
         </is>
       </c>
       <c r="R103" t="n">
@@ -7504,12 +7480,10 @@
       <c r="O104" s="2" t="n">
         <v>415.3891970836409</v>
       </c>
-      <c r="P104" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P104" s="2"/>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">415.389 ± 0</t>
+          <t xml:space="preserve">415.389</t>
         </is>
       </c>
       <c r="R104" s="2" t="n">
@@ -7575,12 +7549,10 @@
       <c r="O105" t="n">
         <v>339.0231341867594</v>
       </c>
-      <c r="P105" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P105"/>
       <c r="Q105" t="inlineStr">
         <is>
-          <t xml:space="preserve">339.023 ± 0</t>
+          <t xml:space="preserve">339.023</t>
         </is>
       </c>
       <c r="R105" t="n">
@@ -7646,12 +7618,10 @@
       <c r="O106" s="2" t="n">
         <v>0.939812263271673</v>
       </c>
-      <c r="P106" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P106" s="2"/>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.939812 ± 0</t>
+          <t xml:space="preserve">0.939812</t>
         </is>
       </c>
       <c r="R106" s="2" t="n">
@@ -9492,12 +9462,10 @@
       <c r="O132" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P132" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P132" s="2"/>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ± 0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="R132" s="2" t="n">
@@ -10202,12 +10170,10 @@
       <c r="O142" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P142" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P142" s="2"/>
       <c r="Q142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ± 0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="R142" s="2" t="n">
@@ -10273,12 +10239,10 @@
       <c r="O143" t="n">
         <v>33.30069609009472</v>
       </c>
-      <c r="P143" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P143"/>
       <c r="Q143" t="inlineStr">
         <is>
-          <t xml:space="preserve">33.3007 ± 0</t>
+          <t xml:space="preserve">33.3007</t>
         </is>
       </c>
       <c r="R143" t="n">
@@ -10344,12 +10308,10 @@
       <c r="O144" s="2" t="n">
         <v>33.30069609009472</v>
       </c>
-      <c r="P144" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P144" s="2"/>
       <c r="Q144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33.3007 ± 0</t>
+          <t xml:space="preserve">33.3007</t>
         </is>
       </c>
       <c r="R144" s="2" t="n">
@@ -10415,12 +10377,10 @@
       <c r="O145" t="n">
         <v>15.28110329348659</v>
       </c>
-      <c r="P145" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P145"/>
       <c r="Q145" t="inlineStr">
         <is>
-          <t xml:space="preserve">15.2811 ± 0</t>
+          <t xml:space="preserve">15.2811</t>
         </is>
       </c>
       <c r="R145" t="n">
@@ -10486,12 +10446,10 @@
       <c r="O146" s="2" t="n">
         <v>0.8206064033763386</v>
       </c>
-      <c r="P146" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P146" s="2"/>
       <c r="Q146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.820606 ± 0</t>
+          <t xml:space="preserve">0.820606</t>
         </is>
       </c>
       <c r="R146" s="2" t="n">
@@ -11622,12 +11580,10 @@
       <c r="O162" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P162" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P162" s="2"/>
       <c r="Q162" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ± 0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="R162" s="2" t="n">
@@ -13042,12 +12998,10 @@
       <c r="O182" s="2" t="n">
         <v>0.5802469135802469</v>
       </c>
-      <c r="P182" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P182" s="2"/>
       <c r="Q182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.580247 ± 0</t>
+          <t xml:space="preserve">0.580247</t>
         </is>
       </c>
       <c r="R182" s="2" t="n">
@@ -13113,12 +13067,10 @@
       <c r="O183" t="n">
         <v>6.261048531659883</v>
       </c>
-      <c r="P183" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P183"/>
       <c r="Q183" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.26105 ± 0</t>
+          <t xml:space="preserve">6.26105</t>
         </is>
       </c>
       <c r="R183" t="n">
@@ -13184,12 +13136,10 @@
       <c r="O184" s="2" t="n">
         <v>6.261048531659883</v>
       </c>
-      <c r="P184" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P184" s="2"/>
       <c r="Q184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.26105 ± 0</t>
+          <t xml:space="preserve">6.26105</t>
         </is>
       </c>
       <c r="R184" s="2" t="n">
@@ -13255,12 +13205,10 @@
       <c r="O185" t="n">
         <v>5.766275112270799</v>
       </c>
-      <c r="P185" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P185"/>
       <c r="Q185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.76628 ± 0</t>
+          <t xml:space="preserve">5.76628</t>
         </is>
       </c>
       <c r="R185" t="n">
@@ -13326,12 +13274,10 @@
       <c r="O186" s="2" t="n">
         <v>0.9203966264408556</v>
       </c>
-      <c r="P186" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P186" s="2"/>
       <c r="Q186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.920397 ± 0</t>
+          <t xml:space="preserve">0.920397</t>
         </is>
       </c>
       <c r="R186" s="2" t="n">
@@ -15882,12 +15828,10 @@
       <c r="O222" s="2" t="n">
         <v>0.9422222222222223</v>
       </c>
-      <c r="P222" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P222" s="2"/>
       <c r="Q222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.942222 ± 0</t>
+          <t xml:space="preserve">0.942222</t>
         </is>
       </c>
       <c r="R222" s="2" t="n">
@@ -16095,12 +16039,10 @@
       <c r="O225" t="n">
         <v>15565.66017557031</v>
       </c>
-      <c r="P225" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P225"/>
       <c r="Q225" t="inlineStr">
         <is>
-          <t xml:space="preserve">15565.7 ± 0</t>
+          <t xml:space="preserve">15565.7</t>
         </is>
       </c>
       <c r="R225" t="n">
@@ -16166,12 +16108,10 @@
       <c r="O226" s="2" t="n">
         <v>0.9999401502175033</v>
       </c>
-      <c r="P226" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="P226" s="2"/>
       <c r="Q226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.99994 ± 0</t>
+          <t xml:space="preserve">0.99994</t>
         </is>
       </c>
       <c r="R226" s="2" t="n">
